--- a/uploads/gen_companies.xlsx
+++ b/uploads/gen_companies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fproject\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C76C488-7C94-45B9-A7E1-EA61306EBEA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5EBA2D-2EBF-4517-8A0B-23F1582585EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13155" yWindow="5835" windowWidth="21600" windowHeight="11385" xr2:uid="{A242F217-D654-450E-8299-EB8E744E1F97}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A242F217-D654-450E-8299-EB8E744E1F97}"/>
   </bookViews>
   <sheets>
     <sheet name="Генерирующая компания" sheetId="1" r:id="rId1"/>
@@ -1534,12 +1534,6 @@
     <t>ФГУП «РФЯЦ-ВНИИТФ имени академика Е. И. Забабахина»</t>
   </si>
   <si>
-    <t>Филиал АО «Группа «Илим» в Братске»</t>
-  </si>
-  <si>
-    <t>Филиал АО «Группа «Илим» в Усть-Илимске»</t>
-  </si>
-  <si>
     <t>Филиал АО «Каустик» – «Волгоградская ТЭЦ-3»</t>
   </si>
   <si>
@@ -1558,7 +1552,13 @@
     <t xml:space="preserve"> МОФ "Мечел-Энерго"</t>
   </si>
   <si>
-    <t>Филиал АО «Группа «Илим» в г. Коряжме»</t>
+    <t>Филиал АО «Группа «Илим» в г. Коряжме</t>
+  </si>
+  <si>
+    <t>Филиал АО «Группа «Илим» в Братске</t>
+  </si>
+  <si>
+    <t>Филиал АО «Группа «Илим» в Усть-Илимске</t>
   </si>
 </sst>
 </file>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -5942,7 +5942,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
@@ -5950,7 +5950,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
@@ -5958,7 +5958,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
@@ -5966,7 +5966,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
@@ -5974,7 +5974,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.25">
@@ -5982,7 +5982,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.25">
@@ -5990,7 +5990,7 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/gen_companies.xlsx
+++ b/uploads/gen_companies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\fproject\uploads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5EBA2D-2EBF-4517-8A0B-23F1582585EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2DC5130-02B7-4A77-862C-5ED3C213771D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{A242F217-D654-450E-8299-EB8E744E1F97}"/>
+    <workbookView xWindow="32760" yWindow="4215" windowWidth="21600" windowHeight="11385" xr2:uid="{A242F217-D654-450E-8299-EB8E744E1F97}"/>
   </bookViews>
   <sheets>
     <sheet name="Генерирующая компания" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="506">
   <si>
     <t>id</t>
   </si>
@@ -181,15 +181,9 @@
     <t>АО «Златмаш»</t>
   </si>
   <si>
-    <t>АО «Интер РАО - Электрогенерация»</t>
-  </si>
-  <si>
     <t>АО «Интер РАО – Электрогенерация»</t>
   </si>
   <si>
-    <t>АО «Интер РАО-Электрогенерация»</t>
-  </si>
-  <si>
     <t>АО «Кавказцемент»</t>
   </si>
   <si>
@@ -271,9 +265,6 @@
     <t>АО «Мобильные ГТЭС»</t>
   </si>
   <si>
-    <t>АО «Монди СЛПК»</t>
-  </si>
-  <si>
     <t>АО «Мордовцемент»</t>
   </si>
   <si>
@@ -1559,6 +1550,9 @@
   </si>
   <si>
     <t>Филиал АО «Группа «Илим» в Усть-Илимске</t>
+  </si>
+  <si>
+    <t>АО «СЛПК»</t>
   </si>
 </sst>
 </file>
@@ -1930,7 +1924,7 @@
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" style="1" bestFit="1" customWidth="1"/>
@@ -1942,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1950,7 +1944,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2558,7 +2552,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>505</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2566,7 +2560,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2574,7 +2568,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
@@ -2582,7 +2576,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
@@ -2590,7 +2584,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
@@ -2598,7 +2592,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
@@ -2606,7 +2600,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
@@ -2614,7 +2608,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
@@ -2622,7 +2616,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
@@ -2630,7 +2624,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
@@ -2638,7 +2632,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -2646,7 +2640,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
@@ -2654,7 +2648,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
@@ -2662,7 +2656,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
@@ -2670,7 +2664,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
@@ -2678,7 +2672,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
@@ -2686,7 +2680,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
@@ -2694,7 +2688,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
@@ -2702,7 +2696,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
@@ -2710,7 +2704,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
@@ -2718,7 +2712,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
@@ -2726,7 +2720,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
@@ -2734,7 +2728,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
@@ -2742,7 +2736,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
@@ -2750,7 +2744,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
@@ -2758,7 +2752,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
@@ -2766,7 +2760,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
@@ -2774,7 +2768,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
@@ -2782,7 +2776,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
@@ -2790,7 +2784,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
@@ -2798,7 +2792,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
@@ -2806,7 +2800,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
@@ -2814,7 +2808,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
@@ -2822,7 +2816,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
@@ -2830,7 +2824,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
@@ -2838,7 +2832,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
@@ -2846,7 +2840,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
@@ -2854,7 +2848,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
@@ -2862,7 +2856,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
@@ -2870,7 +2864,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
@@ -2878,7 +2872,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
@@ -2886,7 +2880,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
@@ -2894,7 +2888,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
@@ -2902,7 +2896,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
@@ -2910,7 +2904,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
@@ -2918,7 +2912,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
@@ -2926,7 +2920,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
@@ -2934,7 +2928,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
@@ -2942,7 +2936,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
@@ -2950,7 +2944,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
@@ -2958,7 +2952,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -2966,7 +2960,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
@@ -2974,7 +2968,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
@@ -2982,7 +2976,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -2990,7 +2984,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
@@ -2998,7 +2992,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
@@ -3006,7 +3000,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
@@ -3014,7 +3008,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
@@ -3022,7 +3016,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
@@ -3030,7 +3024,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
@@ -3038,7 +3032,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
@@ -3046,7 +3040,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
@@ -3054,7 +3048,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
@@ -3062,7 +3056,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
@@ -3070,7 +3064,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
@@ -3078,7 +3072,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
@@ -3086,7 +3080,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
@@ -3094,7 +3088,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
@@ -3102,7 +3096,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
@@ -3110,7 +3104,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
@@ -3118,7 +3112,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
@@ -3126,7 +3120,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
@@ -3134,7 +3128,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
@@ -3142,7 +3136,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
@@ -3150,7 +3144,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
@@ -3158,7 +3152,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
@@ -3166,7 +3160,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
@@ -3174,7 +3168,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
@@ -3182,7 +3176,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
@@ -3190,7 +3184,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
@@ -3198,7 +3192,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
@@ -3206,7 +3200,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
@@ -3214,7 +3208,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
@@ -3222,7 +3216,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
@@ -3230,7 +3224,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
@@ -3238,7 +3232,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
@@ -3246,7 +3240,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
@@ -3254,7 +3248,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
@@ -3262,7 +3256,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
@@ -3270,7 +3264,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
@@ -3278,7 +3272,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
@@ -3286,7 +3280,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
@@ -3294,7 +3288,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
@@ -3302,7 +3296,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
@@ -3310,7 +3304,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
@@ -3318,7 +3312,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
@@ -3326,7 +3320,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
@@ -3334,7 +3328,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
@@ -3342,7 +3336,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
@@ -3350,7 +3344,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
@@ -3358,7 +3352,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
@@ -3366,7 +3360,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
@@ -3374,7 +3368,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
@@ -3382,7 +3376,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
@@ -3390,7 +3384,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
@@ -3398,7 +3392,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
@@ -3406,7 +3400,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
@@ -3414,7 +3408,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
@@ -3422,7 +3416,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
@@ -3430,7 +3424,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
@@ -3438,7 +3432,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
@@ -3446,7 +3440,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
@@ -3454,7 +3448,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
@@ -3462,7 +3456,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
@@ -3470,7 +3464,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
@@ -3478,7 +3472,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
@@ -3486,7 +3480,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
@@ -3494,7 +3488,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
@@ -3502,7 +3496,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
@@ -3510,7 +3504,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
@@ -3518,7 +3512,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
@@ -3526,7 +3520,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
@@ -3534,7 +3528,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
@@ -3542,7 +3536,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
@@ -3550,7 +3544,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
@@ -3558,7 +3552,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
@@ -3566,7 +3560,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
@@ -3574,7 +3568,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
@@ -3582,7 +3576,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
@@ -3590,7 +3584,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
@@ -3598,7 +3592,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
@@ -3606,7 +3600,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
@@ -3614,7 +3608,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
@@ -3622,7 +3616,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
@@ -3630,7 +3624,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
@@ -3638,7 +3632,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
@@ -3646,7 +3640,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
@@ -3654,7 +3648,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
@@ -3662,7 +3656,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
@@ -3670,7 +3664,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
@@ -3678,7 +3672,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
@@ -3686,7 +3680,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
@@ -3694,7 +3688,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
@@ -3702,7 +3696,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
@@ -3710,7 +3704,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
@@ -3718,7 +3712,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
@@ -3726,7 +3720,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
@@ -3734,7 +3728,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
@@ -3742,7 +3736,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
@@ -3750,7 +3744,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
@@ -3758,7 +3752,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.25">
@@ -3766,7 +3760,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.25">
@@ -3774,7 +3768,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.25">
@@ -3782,7 +3776,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.25">
@@ -3790,7 +3784,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.25">
@@ -3798,7 +3792,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.25">
@@ -3806,7 +3800,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.25">
@@ -3814,7 +3808,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.25">
@@ -3822,7 +3816,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.25">
@@ -3830,7 +3824,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.25">
@@ -3838,7 +3832,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.25">
@@ -3846,7 +3840,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.25">
@@ -3854,7 +3848,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.25">
@@ -3862,7 +3856,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.25">
@@ -3870,7 +3864,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.25">
@@ -3878,7 +3872,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.25">
@@ -3886,7 +3880,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.25">
@@ -3894,7 +3888,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.25">
@@ -3902,7 +3896,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.25">
@@ -3910,7 +3904,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.25">
@@ -3918,7 +3912,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.25">
@@ -3926,7 +3920,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.25">
@@ -3934,7 +3928,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.25">
@@ -3942,7 +3936,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.25">
@@ -3950,7 +3944,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.25">
@@ -3958,7 +3952,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.25">
@@ -3966,7 +3960,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.25">
@@ -3974,7 +3968,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.25">
@@ -3982,7 +3976,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.25">
@@ -3990,7 +3984,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.25">
@@ -3998,7 +3992,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.25">
@@ -4006,7 +4000,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.25">
@@ -4014,7 +4008,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.25">
@@ -4022,7 +4016,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.25">
@@ -4030,7 +4024,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.25">
@@ -4038,7 +4032,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.25">
@@ -4046,7 +4040,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.25">
@@ -4054,7 +4048,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.25">
@@ -4062,7 +4056,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.25">
@@ -4070,7 +4064,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.25">
@@ -4078,7 +4072,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.25">
@@ -4086,7 +4080,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.25">
@@ -4094,7 +4088,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.25">
@@ -4102,7 +4096,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.25">
@@ -4110,7 +4104,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.25">
@@ -4118,7 +4112,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.25">
@@ -4126,7 +4120,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.25">
@@ -4134,7 +4128,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.25">
@@ -4142,7 +4136,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.25">
@@ -4150,7 +4144,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.25">
@@ -4158,7 +4152,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.25">
@@ -4166,7 +4160,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.25">
@@ -4174,7 +4168,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.25">
@@ -4182,7 +4176,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.25">
@@ -4190,7 +4184,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.25">
@@ -4198,7 +4192,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.25">
@@ -4206,7 +4200,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.25">
@@ -4214,7 +4208,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.25">
@@ -4222,7 +4216,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.25">
@@ -4230,7 +4224,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.25">
@@ -4238,7 +4232,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
@@ -4246,7 +4240,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
@@ -4254,7 +4248,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
@@ -4262,7 +4256,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
@@ -4270,7 +4264,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.25">
@@ -4278,7 +4272,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.25">
@@ -4286,7 +4280,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.25">
@@ -4294,7 +4288,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.25">
@@ -4302,7 +4296,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.25">
@@ -4310,7 +4304,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.25">
@@ -4318,7 +4312,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.25">
@@ -4326,7 +4320,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.25">
@@ -4334,7 +4328,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.25">
@@ -4342,7 +4336,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.25">
@@ -4350,7 +4344,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.25">
@@ -4358,7 +4352,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.25">
@@ -4366,7 +4360,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.25">
@@ -4374,7 +4368,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.25">
@@ -4382,7 +4376,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.25">
@@ -4390,7 +4384,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.25">
@@ -4398,7 +4392,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.25">
@@ -4406,7 +4400,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.25">
@@ -4414,7 +4408,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.25">
@@ -4422,7 +4416,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.25">
@@ -4430,7 +4424,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.25">
@@ -4438,7 +4432,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.25">
@@ -4446,7 +4440,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.25">
@@ -4454,7 +4448,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.25">
@@ -4462,7 +4456,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.25">
@@ -4470,7 +4464,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.25">
@@ -4478,7 +4472,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.25">
@@ -4486,7 +4480,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.25">
@@ -4494,7 +4488,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.25">
@@ -4502,7 +4496,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
@@ -4510,7 +4504,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -4518,7 +4512,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.25">
@@ -4526,7 +4520,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
@@ -4534,7 +4528,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
@@ -4542,7 +4536,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -4550,7 +4544,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
@@ -4558,7 +4552,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
@@ -4566,7 +4560,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
@@ -4574,7 +4568,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
@@ -4582,7 +4576,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -4590,7 +4584,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.25">
@@ -4598,7 +4592,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.25">
@@ -4606,7 +4600,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.25">
@@ -4614,7 +4608,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.25">
@@ -4622,7 +4616,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.25">
@@ -4630,7 +4624,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.25">
@@ -4638,7 +4632,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.25">
@@ -4646,7 +4640,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.25">
@@ -4654,7 +4648,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.25">
@@ -4662,7 +4656,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.25">
@@ -4670,7 +4664,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.25">
@@ -4678,7 +4672,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.25">
@@ -4686,7 +4680,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.25">
@@ -4694,7 +4688,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.25">
@@ -4702,7 +4696,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.25">
@@ -4710,7 +4704,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.25">
@@ -4718,7 +4712,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.25">
@@ -4726,7 +4720,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.25">
@@ -4734,7 +4728,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.25">
@@ -4742,7 +4736,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.25">
@@ -4750,7 +4744,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.25">
@@ -4758,7 +4752,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.25">
@@ -4766,7 +4760,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.25">
@@ -4774,7 +4768,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.25">
@@ -4782,7 +4776,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.25">
@@ -4790,7 +4784,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.25">
@@ -4798,7 +4792,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.25">
@@ -4806,7 +4800,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.25">
@@ -4814,7 +4808,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.25">
@@ -4822,7 +4816,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.25">
@@ -4830,7 +4824,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.25">
@@ -4838,7 +4832,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.25">
@@ -4846,7 +4840,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.25">
@@ -4854,7 +4848,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.25">
@@ -4862,7 +4856,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.25">
@@ -4870,7 +4864,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.25">
@@ -4878,7 +4872,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.25">
@@ -4886,7 +4880,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.25">
@@ -4894,7 +4888,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.25">
@@ -4902,7 +4896,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.25">
@@ -4910,7 +4904,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.25">
@@ -4918,7 +4912,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.25">
@@ -4926,7 +4920,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.25">
@@ -4934,7 +4928,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.25">
@@ -4942,7 +4936,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.25">
@@ -4950,7 +4944,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.25">
@@ -4958,7 +4952,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.25">
@@ -4966,7 +4960,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.25">
@@ -4974,7 +4968,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.25">
@@ -4982,7 +4976,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.25">
@@ -4990,7 +4984,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.25">
@@ -4998,7 +4992,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.25">
@@ -5006,7 +5000,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.25">
@@ -5014,7 +5008,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.25">
@@ -5022,7 +5016,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.25">
@@ -5030,7 +5024,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.25">
@@ -5038,7 +5032,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.25">
@@ -5046,7 +5040,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.25">
@@ -5054,7 +5048,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.25">
@@ -5062,7 +5056,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.25">
@@ -5070,7 +5064,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.25">
@@ -5078,7 +5072,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.25">
@@ -5086,7 +5080,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.25">
@@ -5094,7 +5088,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.25">
@@ -5102,7 +5096,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.25">
@@ -5110,7 +5104,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.25">
@@ -5118,7 +5112,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.25">
@@ -5126,7 +5120,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.25">
@@ -5134,7 +5128,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.25">
@@ -5142,7 +5136,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.25">
@@ -5150,7 +5144,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.25">
@@ -5158,7 +5152,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.25">
@@ -5166,7 +5160,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.25">
@@ -5174,7 +5168,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.25">
@@ -5182,7 +5176,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.25">
@@ -5190,7 +5184,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.25">
@@ -5198,7 +5192,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.25">
@@ -5206,7 +5200,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.25">
@@ -5214,7 +5208,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.25">
@@ -5222,7 +5216,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.25">
@@ -5230,7 +5224,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.25">
@@ -5238,7 +5232,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.25">
@@ -5246,7 +5240,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.25">
@@ -5254,7 +5248,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.25">
@@ -5262,7 +5256,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.25">
@@ -5270,7 +5264,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.25">
@@ -5278,7 +5272,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.25">
@@ -5286,7 +5280,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.25">
@@ -5294,7 +5288,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.25">
@@ -5302,7 +5296,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.25">
@@ -5310,7 +5304,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.25">
@@ -5318,7 +5312,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.25">
@@ -5326,7 +5320,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.25">
@@ -5334,7 +5328,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.25">
@@ -5342,7 +5336,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.25">
@@ -5350,7 +5344,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.25">
@@ -5358,7 +5352,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.25">
@@ -5366,7 +5360,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.25">
@@ -5374,7 +5368,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.25">
@@ -5382,7 +5376,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.25">
@@ -5390,7 +5384,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.25">
@@ -5398,7 +5392,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.25">
@@ -5406,7 +5400,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.25">
@@ -5414,7 +5408,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.25">
@@ -5422,7 +5416,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.25">
@@ -5430,7 +5424,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.25">
@@ -5438,7 +5432,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.25">
@@ -5446,7 +5440,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.25">
@@ -5454,7 +5448,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.25">
@@ -5462,7 +5456,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.25">
@@ -5470,7 +5464,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.25">
@@ -5478,7 +5472,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.25">
@@ -5486,7 +5480,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.25">
@@ -5494,7 +5488,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.25">
@@ -5502,7 +5496,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.25">
@@ -5510,7 +5504,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.25">
@@ -5518,7 +5512,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.25">
@@ -5526,7 +5520,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.25">
@@ -5534,7 +5528,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.25">
@@ -5542,7 +5536,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.25">
@@ -5550,7 +5544,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.25">
@@ -5558,7 +5552,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.25">
@@ -5566,7 +5560,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.25">
@@ -5574,7 +5568,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.25">
@@ -5582,7 +5576,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.25">
@@ -5590,7 +5584,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.25">
@@ -5598,7 +5592,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.25">
@@ -5606,7 +5600,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.25">
@@ -5614,7 +5608,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.25">
@@ -5622,7 +5616,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.25">
@@ -5630,7 +5624,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.25">
@@ -5638,7 +5632,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.25">
@@ -5646,7 +5640,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.25">
@@ -5654,7 +5648,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.25">
@@ -5662,7 +5656,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.25">
@@ -5670,7 +5664,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.25">
@@ -5678,7 +5672,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.25">
@@ -5686,7 +5680,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.25">
@@ -5694,7 +5688,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.25">
@@ -5702,7 +5696,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.25">
@@ -5710,7 +5704,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.25">
@@ -5718,7 +5712,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.25">
@@ -5726,7 +5720,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.25">
@@ -5734,7 +5728,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.25">
@@ -5742,7 +5736,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.25">
@@ -5750,7 +5744,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.25">
@@ -5758,7 +5752,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.25">
@@ -5766,7 +5760,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.25">
@@ -5774,7 +5768,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.25">
@@ -5782,7 +5776,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.25">
@@ -5790,7 +5784,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.25">
@@ -5798,7 +5792,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.25">
@@ -5806,7 +5800,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.25">
@@ -5814,7 +5808,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.25">
@@ -5822,7 +5816,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.25">
@@ -5830,7 +5824,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.25">
@@ -5838,7 +5832,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.25">
@@ -5846,7 +5840,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.25">
@@ -5854,7 +5848,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.25">
@@ -5862,7 +5856,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.25">
@@ -5870,7 +5864,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.25">
@@ -5878,7 +5872,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.25">
@@ -5886,7 +5880,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.25">
@@ -5894,7 +5888,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.25">
@@ -5902,7 +5896,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.25">
@@ -5910,7 +5904,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.25">
@@ -5918,7 +5912,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.25">
@@ -5926,7 +5920,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.25">
@@ -5934,7 +5928,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.25">
@@ -5942,7 +5936,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.25">
@@ -5950,7 +5944,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.25">
@@ -5958,7 +5952,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.25">
@@ -5966,7 +5960,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.25">
@@ -5974,23 +5968,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A506" s="1">
-        <v>505</v>
-      </c>
-      <c r="B506" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A507" s="1">
-        <v>506</v>
-      </c>
-      <c r="B507" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
